--- a/tams-common-basicdata/src/main/resources/tpl/ComCoinFundQuotationInfo001MTM.xlsx
+++ b/tams-common-basicdata/src/main/resources/tpl/ComCoinFundQuotationInfo001MTM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\tams\tams-common-basicdata\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitlab\tams\tams-common-basicdata\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -130,12 +130,12 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -250,7 +250,7 @@
     <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="180" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -261,6 +261,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="22">
     <cellStyle name="Normal_SJNS_SD_TPL_WK_RPT_JP" xfId="5"/>
@@ -587,19 +588,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.36328125" customWidth="1"/>
-    <col min="4" max="4" width="13.90625" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125"/>
-    <col min="6" max="6" width="9.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.90625" customWidth="1"/>
+    <col min="1" max="1" width="19.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" customWidth="1"/>
+    <col min="4" max="4" width="13.875" customWidth="1"/>
+    <col min="5" max="5" width="10.375"/>
+    <col min="6" max="6" width="9.75" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="11.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5">
+    <row r="1" spans="1:9" ht="16.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -630,7 +631,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="C2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:9">
       <c r="C3" s="3"/>
@@ -691,15 +692,15 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -709,7 +710,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
